--- a/case_studies/base_case/2040/technologies.xlsx
+++ b/case_studies/base_case/2040/technologies.xlsx
@@ -691,31 +691,31 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0</v>
+        <v>60.57</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>78.38</v>
+        <v>123.21</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>154.25</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>74.08</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>723.41</v>
+        <v>675.16</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>723.41</v>
+        <v>675.16</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>3.16</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>141.82</v>
+        <v>114.1</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
@@ -788,13 +788,13 @@
         <v>0</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>17.2</v>
+        <v>16.16</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>15.76</v>
+        <v>34.09</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>34.39</v>
+        <v>31.27</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>17.2</v>
+        <v>16.16</v>
       </c>
       <c r="U3" s="5" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>-0</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>44.5</v>
+        <v>42.99</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -885,49 +885,49 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>107.07</v>
+        <v>183.78</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>227.76</v>
+        <v>401.46</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>27.59</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1225.29</v>
+        <v>1087.44</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1225.29</v>
+        <v>1087.44</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>184.06</v>
+        <v>435.14</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>171.28</v>
+        <v>407.92</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>207.07</v>
+        <v>183.78</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>0</v>
+        <v>14.73</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>0</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>35.71</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>0</v>
@@ -979,34 +979,34 @@
         <v>38.39</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>12.69</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0</v>
+        <v>80.55</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>36.76</v>
+        <v>191.73</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>144</v>
+        <v>80.45</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>87.91</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>643.22</v>
+        <v>619.27</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>643.22</v>
+        <v>619.27</v>
       </c>
       <c r="O5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>37.53</v>
+        <v>44.46</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>0</v>
+        <v>44.46</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>108.7</v>
+        <v>104.66</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" s="5" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>9.73</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>46.82</v>
+        <v>64.94</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1091,28 +1091,28 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>401.07</v>
+        <v>383.35</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>401.07</v>
+        <v>383.35</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0</v>
+        <v>24.62</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.01</v>
+        <v>24.62</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.01</v>
+        <v>6.68</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>67.78</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0</v>
+        <v>6.68</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0</v>
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0</v>
+        <v>28.85</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>52.65</v>
+        <v>56.19</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
@@ -1197,19 +1197,19 @@
         <v>0</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>37.8</v>
+        <v>73.03</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>48.92</v>
+        <v>0.02</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>13.89</v>
+        <v>0.35</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>0</v>
+        <v>28.85</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>48.92</v>
+        <v>0.02</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>62.81</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>175.49</v>
+        <v>180.95</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1285,28 +1285,28 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>286.35</v>
+        <v>136.33</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>286.35</v>
+        <v>136.33</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>96.94</v>
+        <v>176.17</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>146.16</v>
+        <v>207.79</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>125.44</v>
+        <v>65.42</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>33.32</v>
+        <v>21.34</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>78.3</v>
+        <v>128.36</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
         <v>0.76</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>124.94</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>
